--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486395_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486395_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3548</v>
+        <v>3.3346</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4021</v>
+        <v>4.1353</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0473</v>
+        <v>-0.8007</v>
       </c>
       <c r="G2" t="n">
         <v>2.7813</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0514</v>
+        <v>0.0312</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.2752</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0598</v>
+        <v>0.3064</v>
       </c>
       <c r="V2" t="n">
         <v>0.7395</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0626</v>
+        <v>2.3627</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6655</v>
+        <v>3.1943</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6029</v>
+        <v>-0.8316</v>
       </c>
       <c r="G3" t="n">
-        <v>0.718</v>
+        <v>1.9096</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2775</v>
+        <v>0.6051</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5594</v>
+        <v>1.3045</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6513</v>
+        <v>2.8954</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8098</v>
+        <v>0.657</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8415</v>
+        <v>2.2384</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9333</v>
+        <v>-0.9858</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5324</v>
+        <v>-0.0519</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4009</v>
+        <v>-0.9339</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6496</v>
+        <v>0.3455</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3638</v>
+        <v>0.0613</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2859</v>
+        <v>0.2842</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1745</v>
+        <v>1.3252</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1745</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0206</v>
+        <v>0.5357</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7905</v>
+        <v>1.1694</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7699</v>
+        <v>-0.6337</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9096</v>
+        <v>0.718</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6051</v>
+        <v>1.2775</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3045</v>
+        <v>-0.5594</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8954</v>
+        <v>2.6513</v>
       </c>
       <c r="K4" t="n">
-        <v>0.657</v>
+        <v>1.8098</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2384</v>
+        <v>0.8415</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9858</v>
+        <v>-1.9333</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0519</v>
+        <v>-0.5324</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9339</v>
+        <v>-1.4009</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0034</v>
+        <v>1.1227</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3425</v>
+        <v>0.8676</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3458</v>
+        <v>0.2551</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>-0.1745</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALONSO CUEVAS</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.073</v>
+        <v>0.3588</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9646</v>
+        <v>0.7312</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8916</v>
+        <v>-0.3724</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5077</v>
+        <v>0.8784</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2798</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.228</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.836</v>
+        <v>1.2682</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2806</v>
+        <v>0.8458</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5554</v>
+        <v>0.4224</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.3438</v>
+        <v>-0.3898</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5604</v>
+        <v>-0.0519</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7834</v>
+        <v>-0.3379</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1235</v>
+        <v>0.0454</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1286</v>
+        <v>-0.0144</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9949</v>
+        <v>0.0598</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>A. ALONSO CUEVAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3426</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0607</v>
+        <v>1.6294</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4033</v>
+        <v>-2.2307</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8784</v>
+        <v>-1.5077</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7939000000000001</v>
+        <v>-0.2798</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08450000000000001</v>
+        <v>-1.228</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2682</v>
+        <v>1.836</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8458</v>
+        <v>1.2806</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4224</v>
+        <v>0.5554</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3898</v>
+        <v>-3.3438</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0519</v>
+        <v>-1.5604</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3379</v>
+        <v>-1.7834</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.656</v>
+        <v>0.4491</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2067</v>
       </c>
       <c r="U6" t="n">
-        <v>0.029</v>
+        <v>0.6558</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4702</v>
+        <v>-1.048</v>
       </c>
       <c r="E7" t="n">
-        <v>0.839</v>
+        <v>1.1995</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3092</v>
+        <v>-2.2476</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4428</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.2578</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6165</v>
+        <v>-0.256</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0635</v>
+        <v>-0.0018</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7896</v>
+        <v>-1.4543</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2767</v>
+        <v>0.0586</v>
       </c>
       <c r="F8" t="n">
         <v>-1.5129</v>
@@ -1078,10 +1078,10 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.149</v>
+        <v>0.1863</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.411</v>
+        <v>-0.0757</v>
       </c>
       <c r="U8" t="n">
         <v>0.262</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9768</v>
+        <v>-1.7726</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9819</v>
+        <v>1.0936</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9587</v>
+        <v>-2.8662</v>
       </c>
       <c r="G9" t="n">
         <v>-1.398</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3613</v>
+        <v>-0.1571</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5474</v>
+        <v>-1.8208</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5223</v>
+        <v>0.1735</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0251</v>
+        <v>-1.9943</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2128</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.507</v>
+        <v>0.2196</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0274</v>
+        <v>-0.3317</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5204</v>
+        <v>0.5513</v>
       </c>
       <c r="V10" t="n">
         <v>0.5649999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5591</v>
+        <v>-2.6544</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3563</v>
+        <v>0.271</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2028</v>
+        <v>-2.9254</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8725</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.0424</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.0577</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2621</v>
+        <v>0.0153</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7395</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8415</v>
+        <v>-3.7799</v>
       </c>
       <c r="E12" t="n">
         <v>-1.6938</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1477</v>
+        <v>-2.086</v>
       </c>
       <c r="G12" t="n">
         <v>-4.5743</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4076</v>
+        <v>0.4693</v>
       </c>
       <c r="T12" t="n">
         <v>0.1286</v>
       </c>
       <c r="U12" t="n">
-        <v>0.279</v>
+        <v>0.3407</v>
       </c>
       <c r="V12" t="n">
         <v>0.7602</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5684</v>
+        <v>-5.3601</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5158</v>
+        <v>-3.9376</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0526</v>
+        <v>-1.4225</v>
       </c>
       <c r="G13" t="n">
         <v>-5.2059</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>1.985</v>
+        <v>1.1933</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5997</v>
+        <v>0.1779</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3853</v>
+        <v>1.0154</v>
       </c>
       <c r="V13" t="n">
         <v>-1.13</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.5846</v>
+        <v>-11.8996</v>
       </c>
       <c r="E14" t="n">
-        <v>7.339400000000003</v>
+        <v>8.024400000000002</v>
       </c>
       <c r="F14" t="n">
         <v>-19.924</v>
@@ -1543,16 +1543,16 @@
         <v>-14.1377</v>
       </c>
       <c r="R14" t="n">
-        <v>9.787499999999998</v>
+        <v>9.7875</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9202</v>
+        <v>3.6051</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8291000000000005</v>
+        <v>-0.1441999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.749099999999999</v>
+        <v>3.7493</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9347999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7908</v>
+        <v>5.1993</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2768</v>
+        <v>3.5003</v>
       </c>
       <c r="F15" t="n">
-        <v>1.514</v>
+        <v>1.699</v>
       </c>
       <c r="G15" t="n">
         <v>3.1335</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1697</v>
+        <v>-0.7613</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9589</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2108</v>
+        <v>-0.0258</v>
       </c>
       <c r="V15" t="n">
         <v>1.3045</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0115</v>
+        <v>3.892</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1624</v>
+        <v>3.8271</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1509</v>
+        <v>0.0649</v>
       </c>
       <c r="G16" t="n">
         <v>2.5712</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4726</v>
+        <v>-0.5921</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3509</v>
+        <v>-0.6862</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1217</v>
+        <v>0.094</v>
       </c>
       <c r="V16" t="n">
         <v>0.3904</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2444</v>
+        <v>3.5719</v>
       </c>
       <c r="E17" t="n">
-        <v>5.1774</v>
+        <v>5.2892</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.933</v>
+        <v>-1.7172</v>
       </c>
       <c r="G17" t="n">
         <v>3.1831</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6337</v>
+        <v>-0.3061</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3305</v>
+        <v>-0.2187</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3032</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.315</v>
+        <v>2.1275</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6762</v>
+        <v>2.1926</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3612</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8882</v>
+        <v>-1.2097</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2977</v>
+        <v>-1.2925</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5905</v>
+        <v>0.0829</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7634</v>
+        <v>0.9755</v>
       </c>
       <c r="K18" t="n">
-        <v>0.219</v>
+        <v>-0.5927</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5444</v>
+        <v>1.5682</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8751</v>
+        <v>-2.1852</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.6998</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9539</v>
+        <v>-1.4854</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.161</v>
+        <v>0.0544</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0649</v>
+        <v>-0.1081</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0961</v>
+        <v>0.1625</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9347</v>
+        <v>1.3252</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1467</v>
+        <v>2.0915</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3043</v>
+        <v>2.4527</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1576</v>
+        <v>-0.3612</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2097</v>
+        <v>1.8882</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2925</v>
+        <v>0.2977</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0829</v>
+        <v>1.5905</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9755</v>
+        <v>2.7634</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5927</v>
+        <v>0.219</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5682</v>
+        <v>2.5444</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1852</v>
+        <v>-0.8751</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6998</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4854</v>
+        <v>-0.9539</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0737</v>
+        <v>-0.3845</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0036</v>
+        <v>-0.2884</v>
       </c>
       <c r="U19" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.0961</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3252</v>
+        <v>-0.9347</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ZURBRIGGEN</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.6803</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3527</v>
+        <v>2.8255</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6234</v>
+        <v>-2.1452</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4175</v>
+        <v>2.6612</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2039</v>
+        <v>2.619</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2136</v>
+        <v>0.0422</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2832</v>
+        <v>3.581</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0516</v>
+        <v>2.9873</v>
       </c>
       <c r="L20" t="n">
-        <v>2.3348</v>
+        <v>0.5937</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7007</v>
+        <v>-0.9197</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1523</v>
+        <v>-0.3683</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.5484</v>
+        <v>-0.5514</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0721</v>
+        <v>-0.5804</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4879</v>
+        <v>0.0769</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6743</v>
+        <v>-1.695</v>
       </c>
       <c r="W20" t="n">
-        <v>3.3899</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7156</v>
+        <v>-2.8249</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6933</v>
+        <v>0.5893</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9898</v>
+        <v>-0.8781</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6831</v>
+        <v>1.4674</v>
       </c>
       <c r="G21" t="n">
         <v>1.2016</v>
@@ -2092,13 +2092,13 @@
         <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2484</v>
+        <v>-0.3524</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.822</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5736</v>
+        <v>0.3578</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>F. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2332</v>
+        <v>0.3093</v>
       </c>
       <c r="E22" t="n">
-        <v>2.3785</v>
+        <v>3.2409</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1452</v>
+        <v>-2.9317</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6612</v>
+        <v>-0.4175</v>
       </c>
       <c r="H22" t="n">
-        <v>2.619</v>
+        <v>-0.2039</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0422</v>
+        <v>-0.2136</v>
       </c>
       <c r="J22" t="n">
-        <v>3.581</v>
+        <v>2.2832</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9873</v>
+        <v>-0.0516</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5937</v>
+        <v>2.3348</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9197</v>
+        <v>-2.7007</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3683</v>
+        <v>-0.1523</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5514</v>
+        <v>-2.5484</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9505</v>
+        <v>0.14</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0274</v>
+        <v>-0.0396</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0769</v>
+        <v>0.1796</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.695</v>
+        <v>1.6743</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>3.3899</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.8249</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4314</v>
+        <v>-0.3697</v>
       </c>
       <c r="E23" t="n">
         <v>-0.2055</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2259</v>
+        <v>-0.1642</v>
       </c>
       <c r="G23" t="n">
         <v>0.0311</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4624</v>
+        <v>-0.4008</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2055</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2569</v>
+        <v>-0.1953</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.143</v>
+        <v>-2.0813</v>
       </c>
       <c r="E24" t="n">
         <v>-1.6396</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5033</v>
+        <v>-0.4417</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6241</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3014</v>
+        <v>-0.2397</v>
       </c>
       <c r="T24" t="n">
         <v>-0.3425</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0411</v>
+        <v>0.1027</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.0054</v>
+        <v>-3.4254</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5694</v>
+        <v>-0.6811</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.436</v>
+        <v>-2.7443</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1989</v>
@@ -2404,13 +2404,13 @@
         <v>0.6525</v>
       </c>
       <c r="S25" t="n">
-        <v>0.846</v>
+        <v>0.426</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2776</v>
+        <v>0.1658</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5684</v>
+        <v>0.2602</v>
       </c>
       <c r="V25" t="n">
         <v>-1.13</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>12.5844</v>
+        <v>12.5847</v>
       </c>
       <c r="E26" t="n">
         <v>19.924</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.3394</v>
+        <v>-7.339300000000001</v>
       </c>
       <c r="G26" t="n">
         <v>10.2197</v>
@@ -2473,7 +2473,7 @@
         <v>-12.8416</v>
       </c>
       <c r="P26" t="n">
-        <v>4.3501</v>
+        <v>4.350099999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-9.787699999999999</v>
@@ -2482,16 +2482,16 @@
         <v>14.1379</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.92</v>
+        <v>-2.919999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.7493</v>
+        <v>-3.7492</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8292000000000002</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9346999999999999</v>
+        <v>0.9347000000000003</v>
       </c>
       <c r="W26" t="n">
         <v>7.3861</v>
